--- a/data/OP1/Market Data/OP1_market_data.xlsx
+++ b/data/OP1/Market Data/OP1_market_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/Market Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D917E-B370-4C1E-97E4-9D9899348410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F61FA-75E7-754F-B634-723D69646A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51200" yWindow="620" windowWidth="51200" windowHeight="28180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Growth Factors" sheetId="1" r:id="rId1"/>
@@ -388,12 +388,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -401,7 +401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -409,7 +409,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -425,9 +425,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C1090B-5BAB-4DF9-A5D0-788EE84E9C0B}">
   <dimension ref="A1:Z13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -507,7 +507,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -587,7 +587,7 @@
         <v>98.85560000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -667,7 +667,7 @@
         <v>105.039</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -747,7 +747,7 @@
         <v>101.02120000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -755,79 +755,79 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>44</v>
+        <v>96.25</v>
       </c>
       <c r="D5" s="1">
-        <v>46.62</v>
+        <v>101.98124999999999</v>
       </c>
       <c r="E5" s="1">
-        <v>48.16</v>
+        <v>105.35</v>
       </c>
       <c r="F5" s="1">
-        <v>48.4</v>
+        <v>105.875</v>
       </c>
       <c r="G5" s="1">
-        <v>50.5</v>
+        <v>110.46875</v>
       </c>
       <c r="H5" s="1">
-        <v>55.99</v>
+        <v>122.47812500000001</v>
       </c>
       <c r="I5" s="1">
-        <v>58.82</v>
+        <v>128.66874999999999</v>
       </c>
       <c r="J5" s="1">
-        <v>49.98</v>
+        <v>109.33124999999998</v>
       </c>
       <c r="K5" s="1">
-        <v>33.799999999999997</v>
+        <v>73.937499999999986</v>
       </c>
       <c r="L5" s="1">
-        <v>13.5</v>
+        <v>29.53125</v>
       </c>
       <c r="M5" s="1">
-        <v>11.3</v>
+        <v>24.718750000000004</v>
       </c>
       <c r="N5" s="1">
-        <v>9.4499999999999993</v>
+        <v>20.671874999999996</v>
       </c>
       <c r="O5" s="1">
-        <v>4.5</v>
+        <v>9.84375</v>
       </c>
       <c r="P5" s="1">
-        <v>3.13</v>
+        <v>6.8468749999999998</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.54</v>
+        <v>1.1812500000000001</v>
       </c>
       <c r="R5" s="1">
-        <v>3.25</v>
+        <v>7.109375</v>
       </c>
       <c r="S5" s="1">
-        <v>5</v>
+        <v>10.9375</v>
       </c>
       <c r="T5" s="1">
-        <v>15.17</v>
+        <v>33.184375000000003</v>
       </c>
       <c r="U5" s="1">
-        <v>33.799999999999997</v>
+        <v>73.937499999999986</v>
       </c>
       <c r="V5" s="1">
-        <v>49.12</v>
+        <v>107.44999999999999</v>
       </c>
       <c r="W5" s="1">
-        <v>59.31</v>
+        <v>129.74062499999999</v>
       </c>
       <c r="X5" s="1">
-        <v>57.63</v>
+        <v>126.06562500000001</v>
       </c>
       <c r="Y5" s="1">
-        <v>49</v>
+        <v>107.1875</v>
       </c>
       <c r="Z5" s="1">
-        <v>72.430000000000007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+        <v>158.44062500000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -835,79 +835,79 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>70.5</v>
+        <v>154.21875</v>
       </c>
       <c r="D6" s="1">
-        <v>69.13</v>
+        <v>151.22187499999998</v>
       </c>
       <c r="E6" s="1">
-        <v>69</v>
+        <v>150.9375</v>
       </c>
       <c r="F6" s="1">
-        <v>68.010000000000005</v>
+        <v>148.77187500000002</v>
       </c>
       <c r="G6" s="1">
-        <v>68.84</v>
+        <v>150.58750000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>67</v>
+        <v>146.5625</v>
       </c>
       <c r="I6" s="1">
-        <v>67.92</v>
+        <v>148.57499999999999</v>
       </c>
       <c r="J6" s="1">
-        <v>72.87</v>
+        <v>159.40312500000002</v>
       </c>
       <c r="K6" s="1">
-        <v>41.7</v>
+        <v>91.218750000000014</v>
       </c>
       <c r="L6" s="1">
-        <v>30</v>
+        <v>65.625</v>
       </c>
       <c r="M6" s="1">
-        <v>18.82</v>
+        <v>41.168750000000003</v>
       </c>
       <c r="N6" s="1">
-        <v>20.43</v>
+        <v>44.690624999999997</v>
       </c>
       <c r="O6" s="1">
-        <v>14.7</v>
+        <v>32.15625</v>
       </c>
       <c r="P6" s="1">
-        <v>9.66</v>
+        <v>21.131250000000001</v>
       </c>
       <c r="Q6" s="1">
-        <v>8.2100000000000009</v>
+        <v>17.959375000000001</v>
       </c>
       <c r="R6" s="1">
-        <v>7.44</v>
+        <v>16.275000000000002</v>
       </c>
       <c r="S6" s="1">
-        <v>14.7</v>
+        <v>32.15625</v>
       </c>
       <c r="T6" s="1">
-        <v>19.440000000000001</v>
+        <v>42.525000000000006</v>
       </c>
       <c r="U6" s="1">
-        <v>34.79</v>
+        <v>76.103125000000006</v>
       </c>
       <c r="V6" s="1">
-        <v>62.73</v>
+        <v>137.22187499999998</v>
       </c>
       <c r="W6" s="1">
-        <v>68.010000000000005</v>
+        <v>148.77187500000002</v>
       </c>
       <c r="X6" s="1">
-        <v>66.77</v>
+        <v>146.05937499999999</v>
       </c>
       <c r="Y6" s="1">
-        <v>63.08</v>
+        <v>137.98750000000001</v>
       </c>
       <c r="Z6" s="1">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+        <v>157.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -915,79 +915,79 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>68.900000000000006</v>
+        <v>150.71875000000003</v>
       </c>
       <c r="D7" s="1">
-        <v>65.900000000000006</v>
+        <v>144.15625000000003</v>
       </c>
       <c r="E7" s="1">
-        <v>66.319999999999993</v>
+        <v>145.07499999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>64.760000000000005</v>
+        <v>141.66250000000002</v>
       </c>
       <c r="G7" s="1">
-        <v>67.88</v>
+        <v>148.48749999999998</v>
       </c>
       <c r="H7" s="1">
-        <v>62.9</v>
+        <v>137.59375</v>
       </c>
       <c r="I7" s="1">
-        <v>66.430000000000007</v>
+        <v>145.31562500000001</v>
       </c>
       <c r="J7" s="1">
-        <v>58.58</v>
+        <v>128.14375000000001</v>
       </c>
       <c r="K7" s="1">
-        <v>38.65</v>
+        <v>84.546875</v>
       </c>
       <c r="L7" s="1">
-        <v>24.17</v>
+        <v>52.871875000000003</v>
       </c>
       <c r="M7" s="1">
-        <v>22</v>
+        <v>48.125</v>
       </c>
       <c r="N7" s="1">
-        <v>21.76</v>
+        <v>47.600000000000009</v>
       </c>
       <c r="O7" s="1">
-        <v>11.72</v>
+        <v>25.637500000000003</v>
       </c>
       <c r="P7" s="1">
-        <v>10.23</v>
+        <v>22.378125000000001</v>
       </c>
       <c r="Q7" s="1">
-        <v>3.25</v>
+        <v>7.109375</v>
       </c>
       <c r="R7" s="1">
-        <v>3.25</v>
+        <v>7.109375</v>
       </c>
       <c r="S7" s="1">
-        <v>8.4700000000000006</v>
+        <v>18.528125000000003</v>
       </c>
       <c r="T7" s="1">
-        <v>25.1</v>
+        <v>54.906250000000007</v>
       </c>
       <c r="U7" s="1">
-        <v>41.2</v>
+        <v>90.125000000000014</v>
       </c>
       <c r="V7" s="1">
-        <v>57.24</v>
+        <v>125.21250000000001</v>
       </c>
       <c r="W7" s="1">
-        <v>74.63</v>
+        <v>163.25312499999998</v>
       </c>
       <c r="X7" s="1">
-        <v>67.88</v>
+        <v>148.48749999999998</v>
       </c>
       <c r="Y7" s="1">
-        <v>71</v>
+        <v>155.3125</v>
       </c>
       <c r="Z7" s="1">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+        <v>157.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -995,79 +995,79 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>113.14</v>
+        <v>94.14500000000001</v>
       </c>
       <c r="D8" s="1">
-        <v>112.38</v>
+        <v>95.970624999999984</v>
       </c>
       <c r="E8" s="1">
-        <v>112.64</v>
+        <v>97.71</v>
       </c>
       <c r="F8" s="1">
-        <v>112.58</v>
+        <v>94.847499999999997</v>
       </c>
       <c r="G8" s="1">
-        <v>112.88</v>
+        <v>97.914375000000007</v>
       </c>
       <c r="H8" s="1">
-        <v>116.84</v>
+        <v>106.18406250000001</v>
       </c>
       <c r="I8" s="1">
-        <v>120.72</v>
+        <v>116.40437499999999</v>
       </c>
       <c r="J8" s="1">
-        <v>116.84</v>
+        <v>115.24062499999999</v>
       </c>
       <c r="K8" s="1">
-        <v>112.82</v>
+        <v>97.34375</v>
       </c>
       <c r="L8" s="1">
-        <v>111.92</v>
+        <v>73.78562500000001</v>
       </c>
       <c r="M8" s="1">
-        <v>98</v>
+        <v>62.299374999999998</v>
       </c>
       <c r="N8" s="1">
-        <v>92.98</v>
+        <v>56.995937499999997</v>
       </c>
       <c r="O8" s="1">
-        <v>92.79</v>
+        <v>50.616875</v>
       </c>
       <c r="P8" s="1">
-        <v>88.99</v>
+        <v>48.473437499999996</v>
       </c>
       <c r="Q8" s="1">
-        <v>83</v>
+        <v>46.790625000000006</v>
       </c>
       <c r="R8" s="1">
-        <v>81.8</v>
+        <v>58.3746875</v>
       </c>
       <c r="S8" s="1">
-        <v>81.8</v>
+        <v>65.938749999999999</v>
       </c>
       <c r="T8" s="1">
-        <v>94.37</v>
+        <v>84.212187499999999</v>
       </c>
       <c r="U8" s="1">
-        <v>109.2</v>
+        <v>117.23874999999998</v>
       </c>
       <c r="V8" s="1">
-        <v>117.6</v>
+        <v>129.48500000000001</v>
       </c>
       <c r="W8" s="1">
-        <v>132.66</v>
+        <v>126.3703125</v>
       </c>
       <c r="X8" s="1">
-        <v>125.5</v>
+        <v>122.17281250000001</v>
       </c>
       <c r="Y8" s="1">
-        <v>117.14</v>
+        <v>112.73375</v>
       </c>
       <c r="Z8" s="1">
-        <v>113.84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+        <v>134.0403125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1075,79 +1075,79 @@
         <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>107.22</v>
+        <v>117.109375</v>
       </c>
       <c r="D9" s="1">
-        <v>107.21</v>
+        <v>114.00593749999999</v>
       </c>
       <c r="E9" s="1">
-        <v>107.21</v>
+        <v>112.96875</v>
       </c>
       <c r="F9" s="1">
-        <v>95</v>
+        <v>110.68093750000001</v>
       </c>
       <c r="G9" s="1">
-        <v>102.44</v>
+        <v>110.78874999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>105</v>
+        <v>111.78125</v>
       </c>
       <c r="I9" s="1">
-        <v>115.1</v>
+        <v>118.48249999999999</v>
       </c>
       <c r="J9" s="1">
-        <v>102.44</v>
+        <v>133.3815625</v>
       </c>
       <c r="K9" s="1">
-        <v>87.97</v>
+        <v>106.39937500000001</v>
       </c>
       <c r="L9" s="1">
-        <v>79.39</v>
+        <v>84.212500000000006</v>
       </c>
       <c r="M9" s="1">
-        <v>79.599999999999994</v>
+        <v>67.184375000000003</v>
       </c>
       <c r="N9" s="1">
-        <v>81.099999999999994</v>
+        <v>64.865312500000002</v>
       </c>
       <c r="O9" s="1">
-        <v>82</v>
+        <v>60.533124999999998</v>
       </c>
       <c r="P9" s="1">
-        <v>82.49</v>
+        <v>53.220624999999998</v>
       </c>
       <c r="Q9" s="1">
-        <v>79.599999999999994</v>
+        <v>51.734687500000007</v>
       </c>
       <c r="R9" s="1">
-        <v>79.599999999999994</v>
+        <v>55.887500000000003</v>
       </c>
       <c r="S9" s="1">
-        <v>82</v>
+        <v>72.578125</v>
       </c>
       <c r="T9" s="1">
-        <v>84.23</v>
+        <v>86.262500000000003</v>
       </c>
       <c r="U9" s="1">
-        <v>89</v>
+        <v>105.1215625</v>
       </c>
       <c r="V9" s="1">
-        <v>116.2</v>
+        <v>136.11593749999997</v>
       </c>
       <c r="W9" s="1">
-        <v>128.9</v>
+        <v>148.74593750000003</v>
       </c>
       <c r="X9" s="1">
-        <v>122.42</v>
+        <v>140.19968749999998</v>
       </c>
       <c r="Y9" s="1">
-        <v>115.58</v>
+        <v>126.59375</v>
       </c>
       <c r="Z9" s="1">
-        <v>107.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+        <v>129.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1155,79 +1155,79 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>108.64</v>
+        <v>118.59937500000001</v>
       </c>
       <c r="D10" s="1">
-        <v>104.63</v>
+        <v>112.93312500000002</v>
       </c>
       <c r="E10" s="1">
-        <v>105.25</v>
+        <v>110.03749999999999</v>
       </c>
       <c r="F10" s="1">
-        <v>93.63</v>
+        <v>106.18125000000001</v>
       </c>
       <c r="G10" s="1">
-        <v>94.37</v>
+        <v>109.58374999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>99.45</v>
+        <v>104.626875</v>
       </c>
       <c r="I10" s="1">
-        <v>113.3</v>
+        <v>109.57781250000001</v>
       </c>
       <c r="J10" s="1">
-        <v>109.87</v>
+        <v>103.07187500000001</v>
       </c>
       <c r="K10" s="1">
-        <v>90</v>
+        <v>78.818437500000002</v>
       </c>
       <c r="L10" s="1">
-        <v>75</v>
+        <v>61.435937500000001</v>
       </c>
       <c r="M10" s="1">
-        <v>64.88</v>
+        <v>57.417499999999997</v>
       </c>
       <c r="N10" s="1">
-        <v>64.55</v>
+        <v>47.7</v>
       </c>
       <c r="O10" s="1">
-        <v>64.989999999999995</v>
+        <v>37.813749999999999</v>
       </c>
       <c r="P10" s="1">
-        <v>64.88</v>
+        <v>36.309062500000003</v>
       </c>
       <c r="Q10" s="1">
-        <v>63.37</v>
+        <v>33.5546875</v>
       </c>
       <c r="R10" s="1">
-        <v>60</v>
+        <v>38.769687500000003</v>
       </c>
       <c r="S10" s="1">
-        <v>63.91</v>
+        <v>51.144062500000004</v>
       </c>
       <c r="T10" s="1">
-        <v>69.989999999999995</v>
+        <v>80.193125000000009</v>
       </c>
       <c r="U10" s="1">
-        <v>85.53</v>
+        <v>108.0025</v>
       </c>
       <c r="V10" s="1">
-        <v>109.02</v>
+        <v>122.61125000000001</v>
       </c>
       <c r="W10" s="1">
-        <v>114.26</v>
+        <v>141.4765625</v>
       </c>
       <c r="X10" s="1">
-        <v>108.54</v>
+        <v>129.61874999999998</v>
       </c>
       <c r="Y10" s="1">
-        <v>94.18</v>
+        <v>128.20125000000002</v>
       </c>
       <c r="Z10" s="1">
-        <v>74.23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+        <v>126.575</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>109.64</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1474,10 +1474,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EAE8BD-6C17-44DF-B187-38D65FB995D2}">
-  <dimension ref="A1:Z13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Z16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1565,79 +1565,79 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>61.085759500000016</v>
+        <v>36.651455700000007</v>
       </c>
       <c r="D2" s="1">
-        <v>58.883000000000003</v>
+        <v>35.329799999999999</v>
       </c>
       <c r="E2" s="1">
-        <v>56.819763000000002</v>
+        <v>34.091857800000007</v>
       </c>
       <c r="F2" s="1">
-        <v>59.819576250000004</v>
+        <v>35.891745750000005</v>
       </c>
       <c r="G2" s="1">
-        <v>56.479556000000002</v>
+        <v>33.887733600000004</v>
       </c>
       <c r="H2" s="1">
-        <v>58.073425000000007</v>
+        <v>34.844055000000004</v>
       </c>
       <c r="I2" s="1">
-        <v>63.812423999999993</v>
+        <v>38.287454399999994</v>
       </c>
       <c r="J2" s="1">
-        <v>65.228981500000003</v>
+        <v>39.137388900000005</v>
       </c>
       <c r="K2" s="1">
-        <v>59.574437999999994</v>
+        <v>35.7446628</v>
       </c>
       <c r="L2" s="1">
-        <v>54.074667750000003</v>
+        <v>32.444800650000005</v>
       </c>
       <c r="M2" s="1">
-        <v>46.584177750000009</v>
+        <v>27.950506650000008</v>
       </c>
       <c r="N2" s="1">
-        <v>44.88089025</v>
+        <v>26.928534150000004</v>
       </c>
       <c r="O2" s="1">
-        <v>39.024960000000007</v>
+        <v>23.414976000000006</v>
       </c>
       <c r="P2" s="1">
-        <v>38.759589000000013</v>
+        <v>23.25575340000001</v>
       </c>
       <c r="Q2" s="1">
-        <v>36.339821000000008</v>
+        <v>21.803892600000008</v>
       </c>
       <c r="R2" s="1">
-        <v>37.095548000000008</v>
+        <v>22.257328800000007</v>
       </c>
       <c r="S2" s="1">
-        <v>43.647023750000002</v>
+        <v>26.188214250000001</v>
       </c>
       <c r="T2" s="1">
-        <v>51.411324999999998</v>
+        <v>30.846795</v>
       </c>
       <c r="U2" s="1">
-        <v>63.071325000000009</v>
+        <v>37.84279500000001</v>
       </c>
       <c r="V2" s="1">
-        <v>69.695251749999997</v>
+        <v>41.81715105</v>
       </c>
       <c r="W2" s="1">
-        <v>76.502055000000013</v>
+        <v>45.901233000000012</v>
       </c>
       <c r="X2" s="1">
-        <v>64.269257499999995</v>
+        <v>38.5615545</v>
       </c>
       <c r="Y2" s="1">
-        <v>66.474720000000005</v>
+        <v>39.88483200000001</v>
       </c>
       <c r="Z2" s="1">
-        <v>65.306785500000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+        <v>39.184071300000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1645,79 +1645,79 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>54.792317250000004</v>
+        <v>32.875390350000004</v>
       </c>
       <c r="D3" s="1">
-        <v>57.744225</v>
+        <v>34.646535</v>
       </c>
       <c r="E3" s="1">
-        <v>56.858051249999995</v>
+        <v>34.114830750000003</v>
       </c>
       <c r="F3" s="1">
-        <v>52.676699624999998</v>
+        <v>31.606019775</v>
       </c>
       <c r="G3" s="1">
-        <v>53.288037000000003</v>
+        <v>31.972822200000003</v>
       </c>
       <c r="H3" s="1">
-        <v>56.950306874999995</v>
+        <v>34.170184124999999</v>
       </c>
       <c r="I3" s="1">
-        <v>59.598395999999987</v>
+        <v>35.759037599999992</v>
       </c>
       <c r="J3" s="1">
-        <v>62.127771749999994</v>
+        <v>37.276663049999996</v>
       </c>
       <c r="K3" s="1">
-        <v>58.450391999999994</v>
+        <v>35.070235199999999</v>
       </c>
       <c r="L3" s="1">
-        <v>49.003589250000005</v>
+        <v>29.402153550000005</v>
       </c>
       <c r="M3" s="1">
-        <v>44.826284250000008</v>
+        <v>26.895770550000005</v>
       </c>
       <c r="N3" s="1">
-        <v>41.087017125000003</v>
+        <v>24.652210275000002</v>
       </c>
       <c r="O3" s="1">
-        <v>36.827505000000002</v>
+        <v>22.096503000000002</v>
       </c>
       <c r="P3" s="1">
-        <v>35.834337000000005</v>
+        <v>21.500602200000003</v>
       </c>
       <c r="Q3" s="1">
-        <v>33.247368000000002</v>
+        <v>19.948420800000005</v>
       </c>
       <c r="R3" s="1">
-        <v>36.413487000000003</v>
+        <v>21.848092200000004</v>
       </c>
       <c r="S3" s="1">
-        <v>39.553841250000005</v>
+        <v>23.732304750000004</v>
       </c>
       <c r="T3" s="1">
-        <v>45.615425624999993</v>
+        <v>27.369255374999995</v>
       </c>
       <c r="U3" s="1">
-        <v>57.139050375000004</v>
+        <v>34.283430225000004</v>
       </c>
       <c r="V3" s="1">
-        <v>69.119089875</v>
+        <v>41.471453925000006</v>
       </c>
       <c r="W3" s="1">
-        <v>67.367173500000007</v>
+        <v>40.42030410000001</v>
       </c>
       <c r="X3" s="1">
-        <v>61.920589499999991</v>
+        <v>37.152353699999992</v>
       </c>
       <c r="Y3" s="1">
-        <v>59.100029999999997</v>
+        <v>35.460017999999998</v>
       </c>
       <c r="Z3" s="1">
-        <v>59.761869749999995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+        <v>35.857121849999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1725,79 +1725,79 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>62.883070750000009</v>
+        <v>37.729842450000007</v>
       </c>
       <c r="D4" s="1">
-        <v>57.060960000000001</v>
+        <v>34.236576000000007</v>
       </c>
       <c r="E4" s="1">
-        <v>60.282114749999991</v>
+        <v>36.169268849999995</v>
       </c>
       <c r="F4" s="1">
-        <v>58.083572374999996</v>
+        <v>34.850143424999999</v>
       </c>
       <c r="G4" s="1">
-        <v>61.084695000000011</v>
+        <v>36.650817000000011</v>
       </c>
       <c r="H4" s="1">
-        <v>59.207500374999995</v>
+        <v>35.524500224999997</v>
       </c>
       <c r="I4" s="1">
-        <v>60.698210999999993</v>
+        <v>36.418926599999999</v>
       </c>
       <c r="J4" s="1">
-        <v>64.540500749999993</v>
+        <v>38.724300450000001</v>
       </c>
       <c r="K4" s="1">
-        <v>60.743900000000004</v>
+        <v>36.446340000000006</v>
       </c>
       <c r="L4" s="1">
-        <v>56.746580625000007</v>
+        <v>34.047948375000004</v>
       </c>
       <c r="M4" s="1">
-        <v>48.448610250000009</v>
+        <v>29.069166150000008</v>
       </c>
       <c r="N4" s="1">
-        <v>42.612950625000003</v>
+        <v>25.567770375000006</v>
       </c>
       <c r="O4" s="1">
-        <v>39.803465000000003</v>
+        <v>23.882079000000004</v>
       </c>
       <c r="P4" s="1">
-        <v>39.125245500000013</v>
+        <v>23.47514730000001</v>
       </c>
       <c r="Q4" s="1">
-        <v>36.308336750000002</v>
+        <v>21.785002050000003</v>
       </c>
       <c r="R4" s="1">
-        <v>37.827603000000003</v>
+        <v>22.696561800000001</v>
       </c>
       <c r="S4" s="1">
-        <v>42.75011125000001</v>
+        <v>25.650066750000008</v>
       </c>
       <c r="T4" s="1">
-        <v>50.858410749999997</v>
+        <v>30.51504645</v>
       </c>
       <c r="U4" s="1">
-        <v>63.666337500000012</v>
+        <v>38.199802500000011</v>
       </c>
       <c r="V4" s="1">
-        <v>74.704470874999998</v>
+        <v>44.822682525000005</v>
       </c>
       <c r="W4" s="1">
-        <v>71.340056500000003</v>
+        <v>42.804033900000007</v>
       </c>
       <c r="X4" s="1">
-        <v>64.875571250000007</v>
+        <v>38.925342750000006</v>
       </c>
       <c r="Y4" s="1">
-        <v>65.166209999999992</v>
+        <v>39.099726000000004</v>
       </c>
       <c r="Z4" s="1">
-        <v>65.256999500000006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+        <v>39.154199700000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1805,79 +1805,79 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>65.330999999999989</v>
+        <v>48.998249999999992</v>
       </c>
       <c r="D5" s="1">
-        <v>66.395437499999986</v>
+        <v>49.796578124999989</v>
       </c>
       <c r="E5" s="1">
-        <v>64.843950000000007</v>
+        <v>48.632962500000005</v>
       </c>
       <c r="F5" s="1">
-        <v>63.312375000000003</v>
+        <v>47.484281250000002</v>
       </c>
       <c r="G5" s="1">
-        <v>64.598300000000009</v>
+        <v>48.44872500000001</v>
       </c>
       <c r="H5" s="1">
-        <v>62.763525000000001</v>
+        <v>47.072643749999997</v>
       </c>
       <c r="I5" s="1">
-        <v>67.108387499999992</v>
+        <v>50.331290624999994</v>
       </c>
       <c r="J5" s="1">
-        <v>65.098950000000002</v>
+        <v>48.824212500000002</v>
       </c>
       <c r="K5" s="1">
-        <v>51.123674999999992</v>
+        <v>38.342756249999994</v>
       </c>
       <c r="L5" s="1">
-        <v>40.077600000000004</v>
+        <v>30.058200000000003</v>
       </c>
       <c r="M5" s="1">
-        <v>34.983750000000008</v>
+        <v>26.237812500000004</v>
       </c>
       <c r="N5" s="1">
-        <v>37.009424999999993</v>
+        <v>27.757068749999995</v>
       </c>
       <c r="O5" s="1">
-        <v>34.175874999999998</v>
+        <v>25.63190625</v>
       </c>
       <c r="P5" s="1">
-        <v>34.043624999999999</v>
+        <v>25.532718750000001</v>
       </c>
       <c r="Q5" s="1">
-        <v>29.746250000000003</v>
+        <v>22.309687500000003</v>
       </c>
       <c r="R5" s="1">
-        <v>29.711674999999996</v>
+        <v>22.283756249999996</v>
       </c>
       <c r="S5" s="1">
-        <v>33.264400000000002</v>
+        <v>24.948300000000003</v>
       </c>
       <c r="T5" s="1">
-        <v>38.537500000000001</v>
+        <v>28.903125000000003</v>
       </c>
       <c r="U5" s="1">
-        <v>48.698099999999997</v>
+        <v>36.523574999999994</v>
       </c>
       <c r="V5" s="1">
-        <v>65.268524999999997</v>
+        <v>48.951393749999994</v>
       </c>
       <c r="W5" s="1">
-        <v>70.05461249999999</v>
+        <v>52.540959374999993</v>
       </c>
       <c r="X5" s="1">
-        <v>67.220650000000006</v>
+        <v>50.415487500000005</v>
       </c>
       <c r="Y5" s="1">
-        <v>63.110024999999986</v>
+        <v>47.332518749999991</v>
       </c>
       <c r="Z5" s="1">
-        <v>63.3909375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+        <v>47.543203124999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1885,79 +1885,79 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>65.330999999999989</v>
+        <v>48.998249999999992</v>
       </c>
       <c r="D6" s="1">
-        <v>60.072062499999987</v>
+        <v>45.05404687499999</v>
       </c>
       <c r="E6" s="1">
-        <v>62.936775000000004</v>
+        <v>47.202581250000001</v>
       </c>
       <c r="F6" s="1">
-        <v>61.503450000000001</v>
+        <v>46.127587500000004</v>
       </c>
       <c r="G6" s="1">
-        <v>63.977162500000013</v>
+        <v>47.982871875000008</v>
       </c>
       <c r="H6" s="1">
-        <v>64.031475</v>
+        <v>48.02360625</v>
       </c>
       <c r="I6" s="1">
-        <v>65.7526625</v>
+        <v>49.314496875000003</v>
       </c>
       <c r="J6" s="1">
-        <v>61.907825000000003</v>
+        <v>46.430868750000002</v>
       </c>
       <c r="K6" s="1">
-        <v>50.617499999999993</v>
+        <v>37.963124999999991</v>
       </c>
       <c r="L6" s="1">
-        <v>39.660125000000001</v>
+        <v>29.745093750000002</v>
       </c>
       <c r="M6" s="1">
-        <v>37.193250000000006</v>
+        <v>27.894937500000005</v>
       </c>
       <c r="N6" s="1">
-        <v>34.8324</v>
+        <v>26.124299999999998</v>
       </c>
       <c r="O6" s="1">
-        <v>35.191000000000003</v>
+        <v>26.393250000000002</v>
       </c>
       <c r="P6" s="1">
-        <v>30.801374999999997</v>
+        <v>23.101031249999998</v>
       </c>
       <c r="Q6" s="1">
-        <v>30.936100000000007</v>
+        <v>23.202075000000004</v>
       </c>
       <c r="R6" s="1">
-        <v>30.594199999999997</v>
+        <v>22.945649999999997</v>
       </c>
       <c r="S6" s="1">
-        <v>32.304850000000002</v>
+        <v>24.228637500000001</v>
       </c>
       <c r="T6" s="1">
-        <v>37.381375000000006</v>
+        <v>28.036031250000004</v>
       </c>
       <c r="U6" s="1">
-        <v>47.714299999999994</v>
+        <v>35.785724999999999</v>
       </c>
       <c r="V6" s="1">
-        <v>66.548299999999998</v>
+        <v>49.911225000000002</v>
       </c>
       <c r="W6" s="1">
-        <v>75.110100000000003</v>
+        <v>56.332575000000006</v>
       </c>
       <c r="X6" s="1">
-        <v>65.848799999999997</v>
+        <v>49.386600000000001</v>
       </c>
       <c r="Y6" s="1">
-        <v>66.297399999999982</v>
+        <v>49.723049999999986</v>
       </c>
       <c r="Z6" s="1">
-        <v>63.3909375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+        <v>47.543203124999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1965,79 +1965,79 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>67.252499999999998</v>
+        <v>50.439374999999998</v>
       </c>
       <c r="D7" s="1">
-        <v>65.130762499999989</v>
+        <v>48.848071874999988</v>
       </c>
       <c r="E7" s="1">
-        <v>62.301050000000004</v>
+        <v>46.725787500000003</v>
       </c>
       <c r="F7" s="1">
-        <v>57.282624999999996</v>
+        <v>42.961968749999997</v>
       </c>
       <c r="G7" s="1">
-        <v>60.250337500000015</v>
+        <v>45.187753125000015</v>
       </c>
       <c r="H7" s="1">
-        <v>63.397500000000001</v>
+        <v>47.548124999999999</v>
       </c>
       <c r="I7" s="1">
-        <v>71.175562499999998</v>
+        <v>53.381671874999995</v>
       </c>
       <c r="J7" s="1">
-        <v>64.460724999999996</v>
+        <v>48.345543749999997</v>
       </c>
       <c r="K7" s="1">
-        <v>49.098974999999989</v>
+        <v>36.82423124999999</v>
       </c>
       <c r="L7" s="1">
-        <v>42.582450000000001</v>
+        <v>31.936837500000003</v>
       </c>
       <c r="M7" s="1">
-        <v>38.298000000000002</v>
+        <v>28.723500000000001</v>
       </c>
       <c r="N7" s="1">
-        <v>35.9209125</v>
+        <v>26.940684375</v>
       </c>
       <c r="O7" s="1">
-        <v>33.499124999999999</v>
+        <v>25.124343750000001</v>
       </c>
       <c r="P7" s="1">
-        <v>31.774049999999999</v>
+        <v>23.830537499999998</v>
       </c>
       <c r="Q7" s="1">
-        <v>28.258937500000002</v>
+        <v>21.194203125000001</v>
       </c>
       <c r="R7" s="1">
-        <v>30.005849999999995</v>
+        <v>22.504387499999996</v>
       </c>
       <c r="S7" s="1">
-        <v>31.984999999999999</v>
+        <v>23.98875</v>
       </c>
       <c r="T7" s="1">
-        <v>38.922875000000005</v>
+        <v>29.192156250000004</v>
       </c>
       <c r="U7" s="1">
-        <v>50.665699999999994</v>
+        <v>37.999274999999997</v>
       </c>
       <c r="V7" s="1">
-        <v>62.708975000000002</v>
+        <v>47.03173125</v>
       </c>
       <c r="W7" s="1">
-        <v>73.665675000000007</v>
+        <v>55.249256250000002</v>
       </c>
       <c r="X7" s="1">
-        <v>66.534724999999995</v>
+        <v>49.901043749999999</v>
       </c>
       <c r="Y7" s="1">
-        <v>66.934874999999977</v>
+        <v>50.201156249999983</v>
       </c>
       <c r="Z7" s="1">
-        <v>62.750624999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+        <v>47.062968749999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2045,79 +2045,79 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>73.44</v>
+        <v>48.669403125000002</v>
       </c>
       <c r="D8" s="1">
-        <v>70.869149999999991</v>
+        <v>50.059406249999995</v>
       </c>
       <c r="E8" s="1">
-        <v>68.526862500000007</v>
+        <v>48.1756265625</v>
       </c>
       <c r="F8" s="1">
-        <v>67.360800000000012</v>
+        <v>44.935007812500004</v>
       </c>
       <c r="G8" s="1">
-        <v>67.09</v>
+        <v>46.034109375</v>
       </c>
       <c r="H8" s="1">
-        <v>72.779200000000003</v>
+        <v>46.089337499999999</v>
       </c>
       <c r="I8" s="1">
-        <v>73.089437500000003</v>
+        <v>49.298245312500001</v>
       </c>
       <c r="J8" s="1">
-        <v>79.457499999999996</v>
+        <v>53.410153125000001</v>
       </c>
       <c r="K8" s="1">
-        <v>78.807299999999998</v>
+        <v>50.509124999999997</v>
       </c>
       <c r="L8" s="1">
-        <v>71.036625000000015</v>
+        <v>45.607050000000001</v>
       </c>
       <c r="M8" s="1">
-        <v>64.039424999999994</v>
+        <v>38.972531250000003</v>
       </c>
       <c r="N8" s="1">
-        <v>58.098750000000003</v>
+        <v>37.062595312499994</v>
       </c>
       <c r="O8" s="1">
-        <v>56.995987500000012</v>
+        <v>37.491740624999998</v>
       </c>
       <c r="P8" s="1">
-        <v>54.863687499999997</v>
+        <v>36.815732812500002</v>
       </c>
       <c r="Q8" s="1">
-        <v>55.085749999999997</v>
+        <v>33.677414062500006</v>
       </c>
       <c r="R8" s="1">
-        <v>61.500037500000005</v>
+        <v>36.283931249999995</v>
       </c>
       <c r="S8" s="1">
-        <v>70.221537499999997</v>
+        <v>41.622749999999996</v>
       </c>
       <c r="T8" s="1">
-        <v>75.865475000000004</v>
+        <v>48.528787500000007</v>
       </c>
       <c r="U8" s="1">
-        <v>92.438062500000001</v>
+        <v>53.298084374999995</v>
       </c>
       <c r="V8" s="1">
-        <v>95.543400000000005</v>
+        <v>62.121553124999991</v>
       </c>
       <c r="W8" s="1">
-        <v>91.109750000000005</v>
+        <v>59.194659375000001</v>
       </c>
       <c r="X8" s="1">
-        <v>94.477687500000016</v>
+        <v>58.11962343750001</v>
       </c>
       <c r="Y8" s="1">
-        <v>82.683750000000003</v>
+        <v>51.894173437500001</v>
       </c>
       <c r="Z8" s="1">
-        <v>72.373199999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+        <v>51.643814062499999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2125,79 +2125,79 @@
         <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>74.174399999999991</v>
+        <v>48.918581249999995</v>
       </c>
       <c r="D9" s="1">
-        <v>73.016699999999986</v>
+        <v>47.688140625000003</v>
       </c>
       <c r="E9" s="1">
-        <v>67.820400000000006</v>
+        <v>47.460435937499994</v>
       </c>
       <c r="F9" s="1">
-        <v>66.040000000000006</v>
+        <v>46.041323437500012</v>
       </c>
       <c r="G9" s="1">
-        <v>68.43180000000001</v>
+        <v>45.801182812500002</v>
       </c>
       <c r="H9" s="1">
-        <v>66.481000000000009</v>
+        <v>46.104553125000002</v>
       </c>
       <c r="I9" s="1">
-        <v>80.0137</v>
+        <v>49.543992187500002</v>
       </c>
       <c r="J9" s="1">
-        <v>76.279200000000003</v>
+        <v>51.065043750000001</v>
       </c>
       <c r="K9" s="1">
-        <v>74.260725000000008</v>
+        <v>49.090378124999994</v>
       </c>
       <c r="L9" s="1">
-        <v>71.733062500000017</v>
+        <v>43.392365624999996</v>
       </c>
       <c r="M9" s="1">
-        <v>60.272399999999998</v>
+        <v>40.064906250000007</v>
       </c>
       <c r="N9" s="1">
-        <v>56.355787500000005</v>
+        <v>36.007199999999997</v>
       </c>
       <c r="O9" s="1">
-        <v>59.933925000000009</v>
+        <v>37.635145312500001</v>
       </c>
       <c r="P9" s="1">
-        <v>60.638812499999993</v>
+        <v>34.899421875000002</v>
       </c>
       <c r="Q9" s="1">
-        <v>58.56485</v>
+        <v>34.834846875000004</v>
       </c>
       <c r="R9" s="1">
-        <v>59.636400000000002</v>
+        <v>35.845223437499996</v>
       </c>
       <c r="S9" s="1">
-        <v>67.494487499999991</v>
+        <v>40.974318750000002</v>
       </c>
       <c r="T9" s="1">
-        <v>76.639612499999998</v>
+        <v>45.473915625000011</v>
       </c>
       <c r="U9" s="1">
-        <v>88.036249999999995</v>
+        <v>55.879584375</v>
       </c>
       <c r="V9" s="1">
-        <v>95.543400000000005</v>
+        <v>63.332456249999993</v>
       </c>
       <c r="W9" s="1">
-        <v>99.741200000000006</v>
+        <v>63.86302968750001</v>
       </c>
       <c r="X9" s="1">
-        <v>85.479812500000008</v>
+        <v>55.687982812500003</v>
       </c>
       <c r="Y9" s="1">
-        <v>83.5105875</v>
+        <v>53.683710937499995</v>
       </c>
       <c r="Z9" s="1">
-        <v>76.142637500000006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+        <v>51.3678515625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2205,79 +2205,79 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>74.908799999999999</v>
+        <v>50.885034375000004</v>
       </c>
       <c r="D10" s="1">
-        <v>74.448399999999992</v>
+        <v>49.10589375</v>
       </c>
       <c r="E10" s="1">
-        <v>70.646250000000009</v>
+        <v>46.758754687500002</v>
       </c>
       <c r="F10" s="1">
-        <v>64.058800000000005</v>
+        <v>44.458514062500001</v>
       </c>
       <c r="G10" s="1">
-        <v>67.760900000000007</v>
+        <v>45.071268750000009</v>
       </c>
       <c r="H10" s="1">
-        <v>67.180800000000005</v>
+        <v>45.866812500000002</v>
       </c>
       <c r="I10" s="1">
-        <v>75.397525000000002</v>
+        <v>52.331723437499996</v>
       </c>
       <c r="J10" s="1">
-        <v>78.662925000000001</v>
+        <v>54.319256249999995</v>
       </c>
       <c r="K10" s="1">
-        <v>79.56506250000001</v>
+        <v>49.442629687499988</v>
       </c>
       <c r="L10" s="1">
-        <v>71.036625000000015</v>
+        <v>45.07627500000001</v>
       </c>
       <c r="M10" s="1">
-        <v>65.922937500000003</v>
+        <v>40.215375000000002</v>
       </c>
       <c r="N10" s="1">
-        <v>60.422700000000006</v>
+        <v>36.176381249999999</v>
       </c>
       <c r="O10" s="1">
-        <v>58.758750000000006</v>
+        <v>37.475226562499998</v>
       </c>
       <c r="P10" s="1">
-        <v>56.018712499999999</v>
+        <v>35.731153124999999</v>
       </c>
       <c r="Q10" s="1">
-        <v>57.405150000000006</v>
+        <v>33.119671875000002</v>
       </c>
       <c r="R10" s="1">
-        <v>63.984887500000006</v>
+        <v>37.677004687499995</v>
       </c>
       <c r="S10" s="1">
-        <v>69.539775000000006</v>
+        <v>39.699974999999995</v>
       </c>
       <c r="T10" s="1">
-        <v>80.510300000000001</v>
+        <v>47.690306250000006</v>
       </c>
       <c r="U10" s="1">
-        <v>85.395162499999984</v>
+        <v>56.61755625</v>
       </c>
       <c r="V10" s="1">
-        <v>93.67</v>
+        <v>61.161721874999998</v>
       </c>
       <c r="W10" s="1">
-        <v>98.782150000000001</v>
+        <v>60.895378125000008</v>
       </c>
       <c r="X10" s="1">
-        <v>91.778325000000009</v>
+        <v>56.264737500000003</v>
       </c>
       <c r="Y10" s="1">
-        <v>78.549562500000008</v>
+        <v>53.625628124999999</v>
       </c>
       <c r="Z10" s="1">
-        <v>79.158187499999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+        <v>50.851771874999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2285,79 +2285,79 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>64.454075000000003</v>
+        <v>48.340556250000006</v>
       </c>
       <c r="D11" s="1">
-        <v>67.09631250000001</v>
+        <v>50.322234375000008</v>
       </c>
       <c r="E11" s="1">
-        <v>63.62438749999999</v>
+        <v>47.718290624999995</v>
       </c>
       <c r="F11" s="1">
-        <v>56.514312500000003</v>
+        <v>42.385734374999998</v>
       </c>
       <c r="G11" s="1">
-        <v>58.159324999999995</v>
+        <v>43.619493749999997</v>
       </c>
       <c r="H11" s="1">
-        <v>60.141375000000011</v>
+        <v>45.106031250000008</v>
       </c>
       <c r="I11" s="1">
-        <v>64.3536</v>
+        <v>48.2652</v>
       </c>
       <c r="J11" s="1">
-        <v>77.328125</v>
+        <v>57.99609375</v>
       </c>
       <c r="K11" s="1">
-        <v>83.567324999999997</v>
+        <v>62.675493750000001</v>
       </c>
       <c r="L11" s="1">
-        <v>81.541200000000003</v>
+        <v>61.155900000000003</v>
       </c>
       <c r="M11" s="1">
-        <v>68.942999999999998</v>
+        <v>51.707250000000002</v>
       </c>
       <c r="N11" s="1">
-        <v>61.8241625</v>
+        <v>46.368121875</v>
       </c>
       <c r="O11" s="1">
-        <v>65.802099999999996</v>
+        <v>49.351574999999997</v>
       </c>
       <c r="P11" s="1">
-        <v>64.131662500000004</v>
+        <v>48.098746875000003</v>
       </c>
       <c r="Q11" s="1">
-        <v>60.060187500000005</v>
+        <v>45.045140625000002</v>
       </c>
       <c r="R11" s="1">
-        <v>67.045474999999996</v>
+        <v>50.284106249999994</v>
       </c>
       <c r="S11" s="1">
-        <v>77.729599999999991</v>
+        <v>58.297199999999989</v>
       </c>
       <c r="T11" s="1">
-        <v>90.87260000000002</v>
+        <v>68.154450000000011</v>
       </c>
       <c r="U11" s="1">
-        <v>93.43012499999999</v>
+        <v>70.072593749999996</v>
       </c>
       <c r="V11" s="1">
-        <v>100.38894999999998</v>
+        <v>75.291712499999988</v>
       </c>
       <c r="W11" s="1">
-        <v>87.797812500000006</v>
+        <v>65.848359375000001</v>
       </c>
       <c r="X11" s="1">
-        <v>87.765012500000012</v>
+        <v>65.823759375000009</v>
       </c>
       <c r="Y11" s="1">
-        <v>75.274437500000019</v>
+        <v>56.455828125000011</v>
       </c>
       <c r="Z11" s="1">
-        <v>74.325900000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+        <v>55.744425000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2365,79 +2365,79 @@
         <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>65.118549999999999</v>
+        <v>48.838912499999999</v>
       </c>
       <c r="D12" s="1">
-        <v>67.09631250000001</v>
+        <v>50.322234375000008</v>
       </c>
       <c r="E12" s="1">
-        <v>63.62438749999999</v>
+        <v>47.718290624999995</v>
       </c>
       <c r="F12" s="1">
-        <v>61.273412500000013</v>
+        <v>45.955059375000012</v>
       </c>
       <c r="G12" s="1">
-        <v>58.159324999999995</v>
+        <v>43.619493749999997</v>
       </c>
       <c r="H12" s="1">
-        <v>58.914000000000009</v>
+        <v>44.185500000000005</v>
       </c>
       <c r="I12" s="1">
-        <v>66.364649999999997</v>
+        <v>49.773487500000002</v>
       </c>
       <c r="J12" s="1">
-        <v>74.265625</v>
+        <v>55.69921875</v>
       </c>
       <c r="K12" s="1">
-        <v>80.290174999999991</v>
+        <v>60.217631249999997</v>
       </c>
       <c r="L12" s="1">
-        <v>76.052849999999992</v>
+        <v>57.039637499999998</v>
       </c>
       <c r="M12" s="1">
-        <v>69.646500000000003</v>
+        <v>52.234875000000002</v>
       </c>
       <c r="N12" s="1">
-        <v>61.186800000000005</v>
+        <v>45.890100000000004</v>
       </c>
       <c r="O12" s="1">
-        <v>65.169387499999999</v>
+        <v>48.877040624999999</v>
       </c>
       <c r="P12" s="1">
-        <v>62.263750000000002</v>
+        <v>46.697812499999998</v>
       </c>
       <c r="Q12" s="1">
-        <v>61.956825000000002</v>
+        <v>46.46761875</v>
       </c>
       <c r="R12" s="1">
-        <v>64.993062499999994</v>
+        <v>48.744796874999992</v>
       </c>
       <c r="S12" s="1">
-        <v>76.959999999999994</v>
+        <v>57.72</v>
       </c>
       <c r="T12" s="1">
-        <v>83.882400000000018</v>
+        <v>62.911800000000014</v>
       </c>
       <c r="U12" s="1">
-        <v>101.29792499999999</v>
+        <v>75.973443750000001</v>
       </c>
       <c r="V12" s="1">
-        <v>102.33824999999999</v>
+        <v>76.753687499999984</v>
       </c>
       <c r="W12" s="1">
-        <v>95.191312500000009</v>
+        <v>71.393484375000014</v>
       </c>
       <c r="X12" s="1">
-        <v>82.652487500000007</v>
+        <v>61.989365625000005</v>
       </c>
       <c r="Y12" s="1">
-        <v>76.859162500000011</v>
+        <v>57.644371875000004</v>
       </c>
       <c r="Z12" s="1">
-        <v>73.59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+        <v>55.192500000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2445,77 +2445,155 @@
         <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>68.440925000000007</v>
+        <v>51.330693750000009</v>
       </c>
       <c r="D13" s="1">
-        <v>65.818287500000011</v>
+        <v>49.363715625000012</v>
       </c>
       <c r="E13" s="1">
-        <v>62.388962499999998</v>
+        <v>46.791721875</v>
       </c>
       <c r="F13" s="1">
-        <v>61.273412500000013</v>
+        <v>45.955059375000012</v>
       </c>
       <c r="G13" s="1">
-        <v>59.939712499999999</v>
+        <v>44.954784375000003</v>
       </c>
       <c r="H13" s="1">
-        <v>58.914000000000009</v>
+        <v>44.185500000000005</v>
       </c>
       <c r="I13" s="1">
-        <v>68.375699999999995</v>
+        <v>51.281774999999996</v>
       </c>
       <c r="J13" s="1">
-        <v>80.390625</v>
+        <v>60.29296875</v>
       </c>
       <c r="K13" s="1">
-        <v>82.748037499999995</v>
+        <v>62.061028124999993</v>
       </c>
       <c r="L13" s="1">
-        <v>77.620950000000008</v>
+        <v>58.215712500000009</v>
       </c>
       <c r="M13" s="1">
-        <v>68.942999999999998</v>
+        <v>51.707250000000002</v>
       </c>
       <c r="N13" s="1">
-        <v>60.549437499999996</v>
+        <v>45.412078124999994</v>
       </c>
       <c r="O13" s="1">
-        <v>66.434812499999992</v>
+        <v>49.826109374999994</v>
       </c>
       <c r="P13" s="1">
-        <v>63.509025000000001</v>
+        <v>47.631768749999999</v>
       </c>
       <c r="Q13" s="1">
-        <v>60.060187500000005</v>
+        <v>45.045140625000002</v>
       </c>
       <c r="R13" s="1">
-        <v>70.466162499999996</v>
+        <v>52.849621874999997</v>
       </c>
       <c r="S13" s="1">
-        <v>73.881599999999992</v>
+        <v>55.411199999999994</v>
       </c>
       <c r="T13" s="1">
-        <v>88.251275000000007</v>
+        <v>66.188456250000002</v>
       </c>
       <c r="U13" s="1">
-        <v>100.31444999999999</v>
+        <v>75.235837500000002</v>
       </c>
       <c r="V13" s="1">
-        <v>100.38894999999998</v>
+        <v>75.291712499999988</v>
       </c>
       <c r="W13" s="1">
-        <v>88.722000000000008</v>
+        <v>66.541500000000013</v>
       </c>
       <c r="X13" s="1">
-        <v>83.504575000000003</v>
+        <v>62.628431250000006</v>
       </c>
       <c r="Y13" s="1">
-        <v>76.066800000000015</v>
+        <v>57.050100000000015</v>
       </c>
       <c r="Z13" s="1">
-        <v>72.854100000000003</v>
-      </c>
+        <v>54.640574999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/OP1/Market Data/OP1_market_data.xlsx
+++ b/data/OP1/Market Data/OP1_market_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP2/Market Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\Market Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3F61FA-75E7-754F-B634-723D69646A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080D917E-B370-4C1E-97E4-9D9899348410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="620" windowWidth="51200" windowHeight="28180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15195" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Growth Factors" sheetId="1" r:id="rId1"/>
@@ -388,12 +388,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -401,7 +401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -409,7 +409,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -425,9 +425,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C1090B-5BAB-4DF9-A5D0-788EE84E9C0B}">
   <dimension ref="A1:Z13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -507,7 +507,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -587,7 +587,7 @@
         <v>98.85560000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -667,7 +667,7 @@
         <v>105.039</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -747,7 +747,7 @@
         <v>101.02120000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -755,79 +755,79 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>96.25</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1">
-        <v>101.98124999999999</v>
+        <v>46.62</v>
       </c>
       <c r="E5" s="1">
-        <v>105.35</v>
+        <v>48.16</v>
       </c>
       <c r="F5" s="1">
-        <v>105.875</v>
+        <v>48.4</v>
       </c>
       <c r="G5" s="1">
-        <v>110.46875</v>
+        <v>50.5</v>
       </c>
       <c r="H5" s="1">
-        <v>122.47812500000001</v>
+        <v>55.99</v>
       </c>
       <c r="I5" s="1">
-        <v>128.66874999999999</v>
+        <v>58.82</v>
       </c>
       <c r="J5" s="1">
-        <v>109.33124999999998</v>
+        <v>49.98</v>
       </c>
       <c r="K5" s="1">
-        <v>73.937499999999986</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="L5" s="1">
-        <v>29.53125</v>
+        <v>13.5</v>
       </c>
       <c r="M5" s="1">
-        <v>24.718750000000004</v>
+        <v>11.3</v>
       </c>
       <c r="N5" s="1">
-        <v>20.671874999999996</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="O5" s="1">
-        <v>9.84375</v>
+        <v>4.5</v>
       </c>
       <c r="P5" s="1">
-        <v>6.8468749999999998</v>
+        <v>3.13</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.1812500000000001</v>
+        <v>0.54</v>
       </c>
       <c r="R5" s="1">
-        <v>7.109375</v>
+        <v>3.25</v>
       </c>
       <c r="S5" s="1">
-        <v>10.9375</v>
+        <v>5</v>
       </c>
       <c r="T5" s="1">
-        <v>33.184375000000003</v>
+        <v>15.17</v>
       </c>
       <c r="U5" s="1">
-        <v>73.937499999999986</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="V5" s="1">
-        <v>107.44999999999999</v>
+        <v>49.12</v>
       </c>
       <c r="W5" s="1">
-        <v>129.74062499999999</v>
+        <v>59.31</v>
       </c>
       <c r="X5" s="1">
-        <v>126.06562500000001</v>
+        <v>57.63</v>
       </c>
       <c r="Y5" s="1">
-        <v>107.1875</v>
+        <v>49</v>
       </c>
       <c r="Z5" s="1">
-        <v>158.44062500000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+        <v>72.430000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -835,79 +835,79 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>154.21875</v>
+        <v>70.5</v>
       </c>
       <c r="D6" s="1">
-        <v>151.22187499999998</v>
+        <v>69.13</v>
       </c>
       <c r="E6" s="1">
-        <v>150.9375</v>
+        <v>69</v>
       </c>
       <c r="F6" s="1">
-        <v>148.77187500000002</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="G6" s="1">
-        <v>150.58750000000001</v>
+        <v>68.84</v>
       </c>
       <c r="H6" s="1">
-        <v>146.5625</v>
+        <v>67</v>
       </c>
       <c r="I6" s="1">
-        <v>148.57499999999999</v>
+        <v>67.92</v>
       </c>
       <c r="J6" s="1">
-        <v>159.40312500000002</v>
+        <v>72.87</v>
       </c>
       <c r="K6" s="1">
-        <v>91.218750000000014</v>
+        <v>41.7</v>
       </c>
       <c r="L6" s="1">
-        <v>65.625</v>
+        <v>30</v>
       </c>
       <c r="M6" s="1">
-        <v>41.168750000000003</v>
+        <v>18.82</v>
       </c>
       <c r="N6" s="1">
-        <v>44.690624999999997</v>
+        <v>20.43</v>
       </c>
       <c r="O6" s="1">
-        <v>32.15625</v>
+        <v>14.7</v>
       </c>
       <c r="P6" s="1">
-        <v>21.131250000000001</v>
+        <v>9.66</v>
       </c>
       <c r="Q6" s="1">
-        <v>17.959375000000001</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="R6" s="1">
-        <v>16.275000000000002</v>
+        <v>7.44</v>
       </c>
       <c r="S6" s="1">
-        <v>32.15625</v>
+        <v>14.7</v>
       </c>
       <c r="T6" s="1">
-        <v>42.525000000000006</v>
+        <v>19.440000000000001</v>
       </c>
       <c r="U6" s="1">
-        <v>76.103125000000006</v>
+        <v>34.79</v>
       </c>
       <c r="V6" s="1">
-        <v>137.22187499999998</v>
+        <v>62.73</v>
       </c>
       <c r="W6" s="1">
-        <v>148.77187500000002</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="X6" s="1">
-        <v>146.05937499999999</v>
+        <v>66.77</v>
       </c>
       <c r="Y6" s="1">
-        <v>137.98750000000001</v>
+        <v>63.08</v>
       </c>
       <c r="Z6" s="1">
-        <v>157.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -915,79 +915,79 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>150.71875000000003</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="D7" s="1">
-        <v>144.15625000000003</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="E7" s="1">
-        <v>145.07499999999999</v>
+        <v>66.319999999999993</v>
       </c>
       <c r="F7" s="1">
-        <v>141.66250000000002</v>
+        <v>64.760000000000005</v>
       </c>
       <c r="G7" s="1">
-        <v>148.48749999999998</v>
+        <v>67.88</v>
       </c>
       <c r="H7" s="1">
-        <v>137.59375</v>
+        <v>62.9</v>
       </c>
       <c r="I7" s="1">
-        <v>145.31562500000001</v>
+        <v>66.430000000000007</v>
       </c>
       <c r="J7" s="1">
-        <v>128.14375000000001</v>
+        <v>58.58</v>
       </c>
       <c r="K7" s="1">
-        <v>84.546875</v>
+        <v>38.65</v>
       </c>
       <c r="L7" s="1">
-        <v>52.871875000000003</v>
+        <v>24.17</v>
       </c>
       <c r="M7" s="1">
-        <v>48.125</v>
+        <v>22</v>
       </c>
       <c r="N7" s="1">
-        <v>47.600000000000009</v>
+        <v>21.76</v>
       </c>
       <c r="O7" s="1">
-        <v>25.637500000000003</v>
+        <v>11.72</v>
       </c>
       <c r="P7" s="1">
-        <v>22.378125000000001</v>
+        <v>10.23</v>
       </c>
       <c r="Q7" s="1">
-        <v>7.109375</v>
+        <v>3.25</v>
       </c>
       <c r="R7" s="1">
-        <v>7.109375</v>
+        <v>3.25</v>
       </c>
       <c r="S7" s="1">
-        <v>18.528125000000003</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="T7" s="1">
-        <v>54.906250000000007</v>
+        <v>25.1</v>
       </c>
       <c r="U7" s="1">
-        <v>90.125000000000014</v>
+        <v>41.2</v>
       </c>
       <c r="V7" s="1">
-        <v>125.21250000000001</v>
+        <v>57.24</v>
       </c>
       <c r="W7" s="1">
-        <v>163.25312499999998</v>
+        <v>74.63</v>
       </c>
       <c r="X7" s="1">
-        <v>148.48749999999998</v>
+        <v>67.88</v>
       </c>
       <c r="Y7" s="1">
-        <v>155.3125</v>
+        <v>71</v>
       </c>
       <c r="Z7" s="1">
-        <v>157.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -995,79 +995,79 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>94.14500000000001</v>
+        <v>113.14</v>
       </c>
       <c r="D8" s="1">
-        <v>95.970624999999984</v>
+        <v>112.38</v>
       </c>
       <c r="E8" s="1">
-        <v>97.71</v>
+        <v>112.64</v>
       </c>
       <c r="F8" s="1">
-        <v>94.847499999999997</v>
+        <v>112.58</v>
       </c>
       <c r="G8" s="1">
-        <v>97.914375000000007</v>
+        <v>112.88</v>
       </c>
       <c r="H8" s="1">
-        <v>106.18406250000001</v>
+        <v>116.84</v>
       </c>
       <c r="I8" s="1">
-        <v>116.40437499999999</v>
+        <v>120.72</v>
       </c>
       <c r="J8" s="1">
-        <v>115.24062499999999</v>
+        <v>116.84</v>
       </c>
       <c r="K8" s="1">
-        <v>97.34375</v>
+        <v>112.82</v>
       </c>
       <c r="L8" s="1">
-        <v>73.78562500000001</v>
+        <v>111.92</v>
       </c>
       <c r="M8" s="1">
-        <v>62.299374999999998</v>
+        <v>98</v>
       </c>
       <c r="N8" s="1">
-        <v>56.995937499999997</v>
+        <v>92.98</v>
       </c>
       <c r="O8" s="1">
-        <v>50.616875</v>
+        <v>92.79</v>
       </c>
       <c r="P8" s="1">
-        <v>48.473437499999996</v>
+        <v>88.99</v>
       </c>
       <c r="Q8" s="1">
-        <v>46.790625000000006</v>
+        <v>83</v>
       </c>
       <c r="R8" s="1">
-        <v>58.3746875</v>
+        <v>81.8</v>
       </c>
       <c r="S8" s="1">
-        <v>65.938749999999999</v>
+        <v>81.8</v>
       </c>
       <c r="T8" s="1">
-        <v>84.212187499999999</v>
+        <v>94.37</v>
       </c>
       <c r="U8" s="1">
-        <v>117.23874999999998</v>
+        <v>109.2</v>
       </c>
       <c r="V8" s="1">
-        <v>129.48500000000001</v>
+        <v>117.6</v>
       </c>
       <c r="W8" s="1">
-        <v>126.3703125</v>
+        <v>132.66</v>
       </c>
       <c r="X8" s="1">
-        <v>122.17281250000001</v>
+        <v>125.5</v>
       </c>
       <c r="Y8" s="1">
-        <v>112.73375</v>
+        <v>117.14</v>
       </c>
       <c r="Z8" s="1">
-        <v>134.0403125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+        <v>113.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1075,79 +1075,79 @@
         <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>117.109375</v>
+        <v>107.22</v>
       </c>
       <c r="D9" s="1">
-        <v>114.00593749999999</v>
+        <v>107.21</v>
       </c>
       <c r="E9" s="1">
-        <v>112.96875</v>
+        <v>107.21</v>
       </c>
       <c r="F9" s="1">
-        <v>110.68093750000001</v>
+        <v>95</v>
       </c>
       <c r="G9" s="1">
-        <v>110.78874999999999</v>
+        <v>102.44</v>
       </c>
       <c r="H9" s="1">
-        <v>111.78125</v>
+        <v>105</v>
       </c>
       <c r="I9" s="1">
-        <v>118.48249999999999</v>
+        <v>115.1</v>
       </c>
       <c r="J9" s="1">
-        <v>133.3815625</v>
+        <v>102.44</v>
       </c>
       <c r="K9" s="1">
-        <v>106.39937500000001</v>
+        <v>87.97</v>
       </c>
       <c r="L9" s="1">
-        <v>84.212500000000006</v>
+        <v>79.39</v>
       </c>
       <c r="M9" s="1">
-        <v>67.184375000000003</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="N9" s="1">
-        <v>64.865312500000002</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="O9" s="1">
-        <v>60.533124999999998</v>
+        <v>82</v>
       </c>
       <c r="P9" s="1">
-        <v>53.220624999999998</v>
+        <v>82.49</v>
       </c>
       <c r="Q9" s="1">
-        <v>51.734687500000007</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="R9" s="1">
-        <v>55.887500000000003</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="S9" s="1">
-        <v>72.578125</v>
+        <v>82</v>
       </c>
       <c r="T9" s="1">
-        <v>86.262500000000003</v>
+        <v>84.23</v>
       </c>
       <c r="U9" s="1">
-        <v>105.1215625</v>
+        <v>89</v>
       </c>
       <c r="V9" s="1">
-        <v>136.11593749999997</v>
+        <v>116.2</v>
       </c>
       <c r="W9" s="1">
-        <v>148.74593750000003</v>
+        <v>128.9</v>
       </c>
       <c r="X9" s="1">
-        <v>140.19968749999998</v>
+        <v>122.42</v>
       </c>
       <c r="Y9" s="1">
-        <v>126.59375</v>
+        <v>115.58</v>
       </c>
       <c r="Z9" s="1">
-        <v>129.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+        <v>107.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1155,79 +1155,79 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>118.59937500000001</v>
+        <v>108.64</v>
       </c>
       <c r="D10" s="1">
-        <v>112.93312500000002</v>
+        <v>104.63</v>
       </c>
       <c r="E10" s="1">
-        <v>110.03749999999999</v>
+        <v>105.25</v>
       </c>
       <c r="F10" s="1">
-        <v>106.18125000000001</v>
+        <v>93.63</v>
       </c>
       <c r="G10" s="1">
-        <v>109.58374999999999</v>
+        <v>94.37</v>
       </c>
       <c r="H10" s="1">
-        <v>104.626875</v>
+        <v>99.45</v>
       </c>
       <c r="I10" s="1">
-        <v>109.57781250000001</v>
+        <v>113.3</v>
       </c>
       <c r="J10" s="1">
-        <v>103.07187500000001</v>
+        <v>109.87</v>
       </c>
       <c r="K10" s="1">
-        <v>78.818437500000002</v>
+        <v>90</v>
       </c>
       <c r="L10" s="1">
-        <v>61.435937500000001</v>
+        <v>75</v>
       </c>
       <c r="M10" s="1">
-        <v>57.417499999999997</v>
+        <v>64.88</v>
       </c>
       <c r="N10" s="1">
-        <v>47.7</v>
+        <v>64.55</v>
       </c>
       <c r="O10" s="1">
-        <v>37.813749999999999</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="P10" s="1">
-        <v>36.309062500000003</v>
+        <v>64.88</v>
       </c>
       <c r="Q10" s="1">
-        <v>33.5546875</v>
+        <v>63.37</v>
       </c>
       <c r="R10" s="1">
-        <v>38.769687500000003</v>
+        <v>60</v>
       </c>
       <c r="S10" s="1">
-        <v>51.144062500000004</v>
+        <v>63.91</v>
       </c>
       <c r="T10" s="1">
-        <v>80.193125000000009</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="U10" s="1">
-        <v>108.0025</v>
+        <v>85.53</v>
       </c>
       <c r="V10" s="1">
-        <v>122.61125000000001</v>
+        <v>109.02</v>
       </c>
       <c r="W10" s="1">
-        <v>141.4765625</v>
+        <v>114.26</v>
       </c>
       <c r="X10" s="1">
-        <v>129.61874999999998</v>
+        <v>108.54</v>
       </c>
       <c r="Y10" s="1">
-        <v>128.20125000000002</v>
+        <v>94.18</v>
       </c>
       <c r="Z10" s="1">
-        <v>126.575</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+        <v>74.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>109.64</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1474,10 +1474,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EAE8BD-6C17-44DF-B187-38D65FB995D2}">
-  <dimension ref="A1:Z16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Z13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1565,79 +1565,79 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>36.651455700000007</v>
+        <v>61.085759500000016</v>
       </c>
       <c r="D2" s="1">
-        <v>35.329799999999999</v>
+        <v>58.883000000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>34.091857800000007</v>
+        <v>56.819763000000002</v>
       </c>
       <c r="F2" s="1">
-        <v>35.891745750000005</v>
+        <v>59.819576250000004</v>
       </c>
       <c r="G2" s="1">
-        <v>33.887733600000004</v>
+        <v>56.479556000000002</v>
       </c>
       <c r="H2" s="1">
-        <v>34.844055000000004</v>
+        <v>58.073425000000007</v>
       </c>
       <c r="I2" s="1">
-        <v>38.287454399999994</v>
+        <v>63.812423999999993</v>
       </c>
       <c r="J2" s="1">
-        <v>39.137388900000005</v>
+        <v>65.228981500000003</v>
       </c>
       <c r="K2" s="1">
-        <v>35.7446628</v>
+        <v>59.574437999999994</v>
       </c>
       <c r="L2" s="1">
-        <v>32.444800650000005</v>
+        <v>54.074667750000003</v>
       </c>
       <c r="M2" s="1">
-        <v>27.950506650000008</v>
+        <v>46.584177750000009</v>
       </c>
       <c r="N2" s="1">
-        <v>26.928534150000004</v>
+        <v>44.88089025</v>
       </c>
       <c r="O2" s="1">
-        <v>23.414976000000006</v>
+        <v>39.024960000000007</v>
       </c>
       <c r="P2" s="1">
-        <v>23.25575340000001</v>
+        <v>38.759589000000013</v>
       </c>
       <c r="Q2" s="1">
-        <v>21.803892600000008</v>
+        <v>36.339821000000008</v>
       </c>
       <c r="R2" s="1">
-        <v>22.257328800000007</v>
+        <v>37.095548000000008</v>
       </c>
       <c r="S2" s="1">
-        <v>26.188214250000001</v>
+        <v>43.647023750000002</v>
       </c>
       <c r="T2" s="1">
-        <v>30.846795</v>
+        <v>51.411324999999998</v>
       </c>
       <c r="U2" s="1">
-        <v>37.84279500000001</v>
+        <v>63.071325000000009</v>
       </c>
       <c r="V2" s="1">
-        <v>41.81715105</v>
+        <v>69.695251749999997</v>
       </c>
       <c r="W2" s="1">
-        <v>45.901233000000012</v>
+        <v>76.502055000000013</v>
       </c>
       <c r="X2" s="1">
-        <v>38.5615545</v>
+        <v>64.269257499999995</v>
       </c>
       <c r="Y2" s="1">
-        <v>39.88483200000001</v>
+        <v>66.474720000000005</v>
       </c>
       <c r="Z2" s="1">
-        <v>39.184071300000006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+        <v>65.306785500000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1645,79 +1645,79 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>32.875390350000004</v>
+        <v>54.792317250000004</v>
       </c>
       <c r="D3" s="1">
-        <v>34.646535</v>
+        <v>57.744225</v>
       </c>
       <c r="E3" s="1">
-        <v>34.114830750000003</v>
+        <v>56.858051249999995</v>
       </c>
       <c r="F3" s="1">
-        <v>31.606019775</v>
+        <v>52.676699624999998</v>
       </c>
       <c r="G3" s="1">
-        <v>31.972822200000003</v>
+        <v>53.288037000000003</v>
       </c>
       <c r="H3" s="1">
-        <v>34.170184124999999</v>
+        <v>56.950306874999995</v>
       </c>
       <c r="I3" s="1">
-        <v>35.759037599999992</v>
+        <v>59.598395999999987</v>
       </c>
       <c r="J3" s="1">
-        <v>37.276663049999996</v>
+        <v>62.127771749999994</v>
       </c>
       <c r="K3" s="1">
-        <v>35.070235199999999</v>
+        <v>58.450391999999994</v>
       </c>
       <c r="L3" s="1">
-        <v>29.402153550000005</v>
+        <v>49.003589250000005</v>
       </c>
       <c r="M3" s="1">
-        <v>26.895770550000005</v>
+        <v>44.826284250000008</v>
       </c>
       <c r="N3" s="1">
-        <v>24.652210275000002</v>
+        <v>41.087017125000003</v>
       </c>
       <c r="O3" s="1">
-        <v>22.096503000000002</v>
+        <v>36.827505000000002</v>
       </c>
       <c r="P3" s="1">
-        <v>21.500602200000003</v>
+        <v>35.834337000000005</v>
       </c>
       <c r="Q3" s="1">
-        <v>19.948420800000005</v>
+        <v>33.247368000000002</v>
       </c>
       <c r="R3" s="1">
-        <v>21.848092200000004</v>
+        <v>36.413487000000003</v>
       </c>
       <c r="S3" s="1">
-        <v>23.732304750000004</v>
+        <v>39.553841250000005</v>
       </c>
       <c r="T3" s="1">
-        <v>27.369255374999995</v>
+        <v>45.615425624999993</v>
       </c>
       <c r="U3" s="1">
-        <v>34.283430225000004</v>
+        <v>57.139050375000004</v>
       </c>
       <c r="V3" s="1">
-        <v>41.471453925000006</v>
+        <v>69.119089875</v>
       </c>
       <c r="W3" s="1">
-        <v>40.42030410000001</v>
+        <v>67.367173500000007</v>
       </c>
       <c r="X3" s="1">
-        <v>37.152353699999992</v>
+        <v>61.920589499999991</v>
       </c>
       <c r="Y3" s="1">
-        <v>35.460017999999998</v>
+        <v>59.100029999999997</v>
       </c>
       <c r="Z3" s="1">
-        <v>35.857121849999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+        <v>59.761869749999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1725,79 +1725,79 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>37.729842450000007</v>
+        <v>62.883070750000009</v>
       </c>
       <c r="D4" s="1">
-        <v>34.236576000000007</v>
+        <v>57.060960000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>36.169268849999995</v>
+        <v>60.282114749999991</v>
       </c>
       <c r="F4" s="1">
-        <v>34.850143424999999</v>
+        <v>58.083572374999996</v>
       </c>
       <c r="G4" s="1">
-        <v>36.650817000000011</v>
+        <v>61.084695000000011</v>
       </c>
       <c r="H4" s="1">
-        <v>35.524500224999997</v>
+        <v>59.207500374999995</v>
       </c>
       <c r="I4" s="1">
-        <v>36.418926599999999</v>
+        <v>60.698210999999993</v>
       </c>
       <c r="J4" s="1">
-        <v>38.724300450000001</v>
+        <v>64.540500749999993</v>
       </c>
       <c r="K4" s="1">
-        <v>36.446340000000006</v>
+        <v>60.743900000000004</v>
       </c>
       <c r="L4" s="1">
-        <v>34.047948375000004</v>
+        <v>56.746580625000007</v>
       </c>
       <c r="M4" s="1">
-        <v>29.069166150000008</v>
+        <v>48.448610250000009</v>
       </c>
       <c r="N4" s="1">
-        <v>25.567770375000006</v>
+        <v>42.612950625000003</v>
       </c>
       <c r="O4" s="1">
-        <v>23.882079000000004</v>
+        <v>39.803465000000003</v>
       </c>
       <c r="P4" s="1">
-        <v>23.47514730000001</v>
+        <v>39.125245500000013</v>
       </c>
       <c r="Q4" s="1">
-        <v>21.785002050000003</v>
+        <v>36.308336750000002</v>
       </c>
       <c r="R4" s="1">
-        <v>22.696561800000001</v>
+        <v>37.827603000000003</v>
       </c>
       <c r="S4" s="1">
-        <v>25.650066750000008</v>
+        <v>42.75011125000001</v>
       </c>
       <c r="T4" s="1">
-        <v>30.51504645</v>
+        <v>50.858410749999997</v>
       </c>
       <c r="U4" s="1">
-        <v>38.199802500000011</v>
+        <v>63.666337500000012</v>
       </c>
       <c r="V4" s="1">
-        <v>44.822682525000005</v>
+        <v>74.704470874999998</v>
       </c>
       <c r="W4" s="1">
-        <v>42.804033900000007</v>
+        <v>71.340056500000003</v>
       </c>
       <c r="X4" s="1">
-        <v>38.925342750000006</v>
+        <v>64.875571250000007</v>
       </c>
       <c r="Y4" s="1">
-        <v>39.099726000000004</v>
+        <v>65.166209999999992</v>
       </c>
       <c r="Z4" s="1">
-        <v>39.154199700000007</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+        <v>65.256999500000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1805,79 +1805,79 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>48.998249999999992</v>
+        <v>65.330999999999989</v>
       </c>
       <c r="D5" s="1">
-        <v>49.796578124999989</v>
+        <v>66.395437499999986</v>
       </c>
       <c r="E5" s="1">
-        <v>48.632962500000005</v>
+        <v>64.843950000000007</v>
       </c>
       <c r="F5" s="1">
-        <v>47.484281250000002</v>
+        <v>63.312375000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>48.44872500000001</v>
+        <v>64.598300000000009</v>
       </c>
       <c r="H5" s="1">
-        <v>47.072643749999997</v>
+        <v>62.763525000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>50.331290624999994</v>
+        <v>67.108387499999992</v>
       </c>
       <c r="J5" s="1">
-        <v>48.824212500000002</v>
+        <v>65.098950000000002</v>
       </c>
       <c r="K5" s="1">
-        <v>38.342756249999994</v>
+        <v>51.123674999999992</v>
       </c>
       <c r="L5" s="1">
-        <v>30.058200000000003</v>
+        <v>40.077600000000004</v>
       </c>
       <c r="M5" s="1">
-        <v>26.237812500000004</v>
+        <v>34.983750000000008</v>
       </c>
       <c r="N5" s="1">
-        <v>27.757068749999995</v>
+        <v>37.009424999999993</v>
       </c>
       <c r="O5" s="1">
-        <v>25.63190625</v>
+        <v>34.175874999999998</v>
       </c>
       <c r="P5" s="1">
-        <v>25.532718750000001</v>
+        <v>34.043624999999999</v>
       </c>
       <c r="Q5" s="1">
-        <v>22.309687500000003</v>
+        <v>29.746250000000003</v>
       </c>
       <c r="R5" s="1">
-        <v>22.283756249999996</v>
+        <v>29.711674999999996</v>
       </c>
       <c r="S5" s="1">
-        <v>24.948300000000003</v>
+        <v>33.264400000000002</v>
       </c>
       <c r="T5" s="1">
-        <v>28.903125000000003</v>
+        <v>38.537500000000001</v>
       </c>
       <c r="U5" s="1">
-        <v>36.523574999999994</v>
+        <v>48.698099999999997</v>
       </c>
       <c r="V5" s="1">
-        <v>48.951393749999994</v>
+        <v>65.268524999999997</v>
       </c>
       <c r="W5" s="1">
-        <v>52.540959374999993</v>
+        <v>70.05461249999999</v>
       </c>
       <c r="X5" s="1">
-        <v>50.415487500000005</v>
+        <v>67.220650000000006</v>
       </c>
       <c r="Y5" s="1">
-        <v>47.332518749999991</v>
+        <v>63.110024999999986</v>
       </c>
       <c r="Z5" s="1">
-        <v>47.543203124999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+        <v>63.3909375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1885,79 +1885,79 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>48.998249999999992</v>
+        <v>65.330999999999989</v>
       </c>
       <c r="D6" s="1">
-        <v>45.05404687499999</v>
+        <v>60.072062499999987</v>
       </c>
       <c r="E6" s="1">
-        <v>47.202581250000001</v>
+        <v>62.936775000000004</v>
       </c>
       <c r="F6" s="1">
-        <v>46.127587500000004</v>
+        <v>61.503450000000001</v>
       </c>
       <c r="G6" s="1">
-        <v>47.982871875000008</v>
+        <v>63.977162500000013</v>
       </c>
       <c r="H6" s="1">
-        <v>48.02360625</v>
+        <v>64.031475</v>
       </c>
       <c r="I6" s="1">
-        <v>49.314496875000003</v>
+        <v>65.7526625</v>
       </c>
       <c r="J6" s="1">
-        <v>46.430868750000002</v>
+        <v>61.907825000000003</v>
       </c>
       <c r="K6" s="1">
-        <v>37.963124999999991</v>
+        <v>50.617499999999993</v>
       </c>
       <c r="L6" s="1">
-        <v>29.745093750000002</v>
+        <v>39.660125000000001</v>
       </c>
       <c r="M6" s="1">
-        <v>27.894937500000005</v>
+        <v>37.193250000000006</v>
       </c>
       <c r="N6" s="1">
-        <v>26.124299999999998</v>
+        <v>34.8324</v>
       </c>
       <c r="O6" s="1">
-        <v>26.393250000000002</v>
+        <v>35.191000000000003</v>
       </c>
       <c r="P6" s="1">
-        <v>23.101031249999998</v>
+        <v>30.801374999999997</v>
       </c>
       <c r="Q6" s="1">
-        <v>23.202075000000004</v>
+        <v>30.936100000000007</v>
       </c>
       <c r="R6" s="1">
-        <v>22.945649999999997</v>
+        <v>30.594199999999997</v>
       </c>
       <c r="S6" s="1">
-        <v>24.228637500000001</v>
+        <v>32.304850000000002</v>
       </c>
       <c r="T6" s="1">
-        <v>28.036031250000004</v>
+        <v>37.381375000000006</v>
       </c>
       <c r="U6" s="1">
-        <v>35.785724999999999</v>
+        <v>47.714299999999994</v>
       </c>
       <c r="V6" s="1">
-        <v>49.911225000000002</v>
+        <v>66.548299999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>56.332575000000006</v>
+        <v>75.110100000000003</v>
       </c>
       <c r="X6" s="1">
-        <v>49.386600000000001</v>
+        <v>65.848799999999997</v>
       </c>
       <c r="Y6" s="1">
-        <v>49.723049999999986</v>
+        <v>66.297399999999982</v>
       </c>
       <c r="Z6" s="1">
-        <v>47.543203124999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+        <v>63.3909375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1965,79 +1965,79 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>50.439374999999998</v>
+        <v>67.252499999999998</v>
       </c>
       <c r="D7" s="1">
-        <v>48.848071874999988</v>
+        <v>65.130762499999989</v>
       </c>
       <c r="E7" s="1">
-        <v>46.725787500000003</v>
+        <v>62.301050000000004</v>
       </c>
       <c r="F7" s="1">
-        <v>42.961968749999997</v>
+        <v>57.282624999999996</v>
       </c>
       <c r="G7" s="1">
-        <v>45.187753125000015</v>
+        <v>60.250337500000015</v>
       </c>
       <c r="H7" s="1">
-        <v>47.548124999999999</v>
+        <v>63.397500000000001</v>
       </c>
       <c r="I7" s="1">
-        <v>53.381671874999995</v>
+        <v>71.175562499999998</v>
       </c>
       <c r="J7" s="1">
-        <v>48.345543749999997</v>
+        <v>64.460724999999996</v>
       </c>
       <c r="K7" s="1">
-        <v>36.82423124999999</v>
+        <v>49.098974999999989</v>
       </c>
       <c r="L7" s="1">
-        <v>31.936837500000003</v>
+        <v>42.582450000000001</v>
       </c>
       <c r="M7" s="1">
-        <v>28.723500000000001</v>
+        <v>38.298000000000002</v>
       </c>
       <c r="N7" s="1">
-        <v>26.940684375</v>
+        <v>35.9209125</v>
       </c>
       <c r="O7" s="1">
-        <v>25.124343750000001</v>
+        <v>33.499124999999999</v>
       </c>
       <c r="P7" s="1">
-        <v>23.830537499999998</v>
+        <v>31.774049999999999</v>
       </c>
       <c r="Q7" s="1">
-        <v>21.194203125000001</v>
+        <v>28.258937500000002</v>
       </c>
       <c r="R7" s="1">
-        <v>22.504387499999996</v>
+        <v>30.005849999999995</v>
       </c>
       <c r="S7" s="1">
-        <v>23.98875</v>
+        <v>31.984999999999999</v>
       </c>
       <c r="T7" s="1">
-        <v>29.192156250000004</v>
+        <v>38.922875000000005</v>
       </c>
       <c r="U7" s="1">
-        <v>37.999274999999997</v>
+        <v>50.665699999999994</v>
       </c>
       <c r="V7" s="1">
-        <v>47.03173125</v>
+        <v>62.708975000000002</v>
       </c>
       <c r="W7" s="1">
-        <v>55.249256250000002</v>
+        <v>73.665675000000007</v>
       </c>
       <c r="X7" s="1">
-        <v>49.901043749999999</v>
+        <v>66.534724999999995</v>
       </c>
       <c r="Y7" s="1">
-        <v>50.201156249999983</v>
+        <v>66.934874999999977</v>
       </c>
       <c r="Z7" s="1">
-        <v>47.062968749999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+        <v>62.750624999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2045,79 +2045,79 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>48.669403125000002</v>
+        <v>73.44</v>
       </c>
       <c r="D8" s="1">
-        <v>50.059406249999995</v>
+        <v>70.869149999999991</v>
       </c>
       <c r="E8" s="1">
-        <v>48.1756265625</v>
+        <v>68.526862500000007</v>
       </c>
       <c r="F8" s="1">
-        <v>44.935007812500004</v>
+        <v>67.360800000000012</v>
       </c>
       <c r="G8" s="1">
-        <v>46.034109375</v>
+        <v>67.09</v>
       </c>
       <c r="H8" s="1">
-        <v>46.089337499999999</v>
+        <v>72.779200000000003</v>
       </c>
       <c r="I8" s="1">
-        <v>49.298245312500001</v>
+        <v>73.089437500000003</v>
       </c>
       <c r="J8" s="1">
-        <v>53.410153125000001</v>
+        <v>79.457499999999996</v>
       </c>
       <c r="K8" s="1">
-        <v>50.509124999999997</v>
+        <v>78.807299999999998</v>
       </c>
       <c r="L8" s="1">
-        <v>45.607050000000001</v>
+        <v>71.036625000000015</v>
       </c>
       <c r="M8" s="1">
-        <v>38.972531250000003</v>
+        <v>64.039424999999994</v>
       </c>
       <c r="N8" s="1">
-        <v>37.062595312499994</v>
+        <v>58.098750000000003</v>
       </c>
       <c r="O8" s="1">
-        <v>37.491740624999998</v>
+        <v>56.995987500000012</v>
       </c>
       <c r="P8" s="1">
-        <v>36.815732812500002</v>
+        <v>54.863687499999997</v>
       </c>
       <c r="Q8" s="1">
-        <v>33.677414062500006</v>
+        <v>55.085749999999997</v>
       </c>
       <c r="R8" s="1">
-        <v>36.283931249999995</v>
+        <v>61.500037500000005</v>
       </c>
       <c r="S8" s="1">
-        <v>41.622749999999996</v>
+        <v>70.221537499999997</v>
       </c>
       <c r="T8" s="1">
-        <v>48.528787500000007</v>
+        <v>75.865475000000004</v>
       </c>
       <c r="U8" s="1">
-        <v>53.298084374999995</v>
+        <v>92.438062500000001</v>
       </c>
       <c r="V8" s="1">
-        <v>62.121553124999991</v>
+        <v>95.543400000000005</v>
       </c>
       <c r="W8" s="1">
-        <v>59.194659375000001</v>
+        <v>91.109750000000005</v>
       </c>
       <c r="X8" s="1">
-        <v>58.11962343750001</v>
+        <v>94.477687500000016</v>
       </c>
       <c r="Y8" s="1">
-        <v>51.894173437500001</v>
+        <v>82.683750000000003</v>
       </c>
       <c r="Z8" s="1">
-        <v>51.643814062499999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+        <v>72.373199999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2125,79 +2125,79 @@
         <v>2</v>
       </c>
       <c r="C9" s="1">
-        <v>48.918581249999995</v>
+        <v>74.174399999999991</v>
       </c>
       <c r="D9" s="1">
-        <v>47.688140625000003</v>
+        <v>73.016699999999986</v>
       </c>
       <c r="E9" s="1">
-        <v>47.460435937499994</v>
+        <v>67.820400000000006</v>
       </c>
       <c r="F9" s="1">
-        <v>46.041323437500012</v>
+        <v>66.040000000000006</v>
       </c>
       <c r="G9" s="1">
-        <v>45.801182812500002</v>
+        <v>68.43180000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>46.104553125000002</v>
+        <v>66.481000000000009</v>
       </c>
       <c r="I9" s="1">
-        <v>49.543992187500002</v>
+        <v>80.0137</v>
       </c>
       <c r="J9" s="1">
-        <v>51.065043750000001</v>
+        <v>76.279200000000003</v>
       </c>
       <c r="K9" s="1">
-        <v>49.090378124999994</v>
+        <v>74.260725000000008</v>
       </c>
       <c r="L9" s="1">
-        <v>43.392365624999996</v>
+        <v>71.733062500000017</v>
       </c>
       <c r="M9" s="1">
-        <v>40.064906250000007</v>
+        <v>60.272399999999998</v>
       </c>
       <c r="N9" s="1">
-        <v>36.007199999999997</v>
+        <v>56.355787500000005</v>
       </c>
       <c r="O9" s="1">
-        <v>37.635145312500001</v>
+        <v>59.933925000000009</v>
       </c>
       <c r="P9" s="1">
-        <v>34.899421875000002</v>
+        <v>60.638812499999993</v>
       </c>
       <c r="Q9" s="1">
-        <v>34.834846875000004</v>
+        <v>58.56485</v>
       </c>
       <c r="R9" s="1">
-        <v>35.845223437499996</v>
+        <v>59.636400000000002</v>
       </c>
       <c r="S9" s="1">
-        <v>40.974318750000002</v>
+        <v>67.494487499999991</v>
       </c>
       <c r="T9" s="1">
-        <v>45.473915625000011</v>
+        <v>76.639612499999998</v>
       </c>
       <c r="U9" s="1">
-        <v>55.879584375</v>
+        <v>88.036249999999995</v>
       </c>
       <c r="V9" s="1">
-        <v>63.332456249999993</v>
+        <v>95.543400000000005</v>
       </c>
       <c r="W9" s="1">
-        <v>63.86302968750001</v>
+        <v>99.741200000000006</v>
       </c>
       <c r="X9" s="1">
-        <v>55.687982812500003</v>
+        <v>85.479812500000008</v>
       </c>
       <c r="Y9" s="1">
-        <v>53.683710937499995</v>
+        <v>83.5105875</v>
       </c>
       <c r="Z9" s="1">
-        <v>51.3678515625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+        <v>76.142637500000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2205,79 +2205,79 @@
         <v>3</v>
       </c>
       <c r="C10" s="1">
-        <v>50.885034375000004</v>
+        <v>74.908799999999999</v>
       </c>
       <c r="D10" s="1">
-        <v>49.10589375</v>
+        <v>74.448399999999992</v>
       </c>
       <c r="E10" s="1">
-        <v>46.758754687500002</v>
+        <v>70.646250000000009</v>
       </c>
       <c r="F10" s="1">
-        <v>44.458514062500001</v>
+        <v>64.058800000000005</v>
       </c>
       <c r="G10" s="1">
-        <v>45.071268750000009</v>
+        <v>67.760900000000007</v>
       </c>
       <c r="H10" s="1">
-        <v>45.866812500000002</v>
+        <v>67.180800000000005</v>
       </c>
       <c r="I10" s="1">
-        <v>52.331723437499996</v>
+        <v>75.397525000000002</v>
       </c>
       <c r="J10" s="1">
-        <v>54.319256249999995</v>
+        <v>78.662925000000001</v>
       </c>
       <c r="K10" s="1">
-        <v>49.442629687499988</v>
+        <v>79.56506250000001</v>
       </c>
       <c r="L10" s="1">
-        <v>45.07627500000001</v>
+        <v>71.036625000000015</v>
       </c>
       <c r="M10" s="1">
-        <v>40.215375000000002</v>
+        <v>65.922937500000003</v>
       </c>
       <c r="N10" s="1">
-        <v>36.176381249999999</v>
+        <v>60.422700000000006</v>
       </c>
       <c r="O10" s="1">
-        <v>37.475226562499998</v>
+        <v>58.758750000000006</v>
       </c>
       <c r="P10" s="1">
-        <v>35.731153124999999</v>
+        <v>56.018712499999999</v>
       </c>
       <c r="Q10" s="1">
-        <v>33.119671875000002</v>
+        <v>57.405150000000006</v>
       </c>
       <c r="R10" s="1">
-        <v>37.677004687499995</v>
+        <v>63.984887500000006</v>
       </c>
       <c r="S10" s="1">
-        <v>39.699974999999995</v>
+        <v>69.539775000000006</v>
       </c>
       <c r="T10" s="1">
-        <v>47.690306250000006</v>
+        <v>80.510300000000001</v>
       </c>
       <c r="U10" s="1">
-        <v>56.61755625</v>
+        <v>85.395162499999984</v>
       </c>
       <c r="V10" s="1">
-        <v>61.161721874999998</v>
+        <v>93.67</v>
       </c>
       <c r="W10" s="1">
-        <v>60.895378125000008</v>
+        <v>98.782150000000001</v>
       </c>
       <c r="X10" s="1">
-        <v>56.264737500000003</v>
+        <v>91.778325000000009</v>
       </c>
       <c r="Y10" s="1">
-        <v>53.625628124999999</v>
+        <v>78.549562500000008</v>
       </c>
       <c r="Z10" s="1">
-        <v>50.851771874999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+        <v>79.158187499999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2285,79 +2285,79 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>48.340556250000006</v>
+        <v>64.454075000000003</v>
       </c>
       <c r="D11" s="1">
-        <v>50.322234375000008</v>
+        <v>67.09631250000001</v>
       </c>
       <c r="E11" s="1">
-        <v>47.718290624999995</v>
+        <v>63.62438749999999</v>
       </c>
       <c r="F11" s="1">
-        <v>42.385734374999998</v>
+        <v>56.514312500000003</v>
       </c>
       <c r="G11" s="1">
-        <v>43.619493749999997</v>
+        <v>58.159324999999995</v>
       </c>
       <c r="H11" s="1">
-        <v>45.106031250000008</v>
+        <v>60.141375000000011</v>
       </c>
       <c r="I11" s="1">
-        <v>48.2652</v>
+        <v>64.3536</v>
       </c>
       <c r="J11" s="1">
-        <v>57.99609375</v>
+        <v>77.328125</v>
       </c>
       <c r="K11" s="1">
-        <v>62.675493750000001</v>
+        <v>83.567324999999997</v>
       </c>
       <c r="L11" s="1">
-        <v>61.155900000000003</v>
+        <v>81.541200000000003</v>
       </c>
       <c r="M11" s="1">
-        <v>51.707250000000002</v>
+        <v>68.942999999999998</v>
       </c>
       <c r="N11" s="1">
-        <v>46.368121875</v>
+        <v>61.8241625</v>
       </c>
       <c r="O11" s="1">
-        <v>49.351574999999997</v>
+        <v>65.802099999999996</v>
       </c>
       <c r="P11" s="1">
-        <v>48.098746875000003</v>
+        <v>64.131662500000004</v>
       </c>
       <c r="Q11" s="1">
-        <v>45.045140625000002</v>
+        <v>60.060187500000005</v>
       </c>
       <c r="R11" s="1">
-        <v>50.284106249999994</v>
+        <v>67.045474999999996</v>
       </c>
       <c r="S11" s="1">
-        <v>58.297199999999989</v>
+        <v>77.729599999999991</v>
       </c>
       <c r="T11" s="1">
-        <v>68.154450000000011</v>
+        <v>90.87260000000002</v>
       </c>
       <c r="U11" s="1">
-        <v>70.072593749999996</v>
+        <v>93.43012499999999</v>
       </c>
       <c r="V11" s="1">
-        <v>75.291712499999988</v>
+        <v>100.38894999999998</v>
       </c>
       <c r="W11" s="1">
-        <v>65.848359375000001</v>
+        <v>87.797812500000006</v>
       </c>
       <c r="X11" s="1">
-        <v>65.823759375000009</v>
+        <v>87.765012500000012</v>
       </c>
       <c r="Y11" s="1">
-        <v>56.455828125000011</v>
+        <v>75.274437500000019</v>
       </c>
       <c r="Z11" s="1">
-        <v>55.744425000000007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+        <v>74.325900000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2365,79 +2365,79 @@
         <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>48.838912499999999</v>
+        <v>65.118549999999999</v>
       </c>
       <c r="D12" s="1">
-        <v>50.322234375000008</v>
+        <v>67.09631250000001</v>
       </c>
       <c r="E12" s="1">
-        <v>47.718290624999995</v>
+        <v>63.62438749999999</v>
       </c>
       <c r="F12" s="1">
-        <v>45.955059375000012</v>
+        <v>61.273412500000013</v>
       </c>
       <c r="G12" s="1">
-        <v>43.619493749999997</v>
+        <v>58.159324999999995</v>
       </c>
       <c r="H12" s="1">
-        <v>44.185500000000005</v>
+        <v>58.914000000000009</v>
       </c>
       <c r="I12" s="1">
-        <v>49.773487500000002</v>
+        <v>66.364649999999997</v>
       </c>
       <c r="J12" s="1">
-        <v>55.69921875</v>
+        <v>74.265625</v>
       </c>
       <c r="K12" s="1">
-        <v>60.217631249999997</v>
+        <v>80.290174999999991</v>
       </c>
       <c r="L12" s="1">
-        <v>57.039637499999998</v>
+        <v>76.052849999999992</v>
       </c>
       <c r="M12" s="1">
-        <v>52.234875000000002</v>
+        <v>69.646500000000003</v>
       </c>
       <c r="N12" s="1">
-        <v>45.890100000000004</v>
+        <v>61.186800000000005</v>
       </c>
       <c r="O12" s="1">
-        <v>48.877040624999999</v>
+        <v>65.169387499999999</v>
       </c>
       <c r="P12" s="1">
-        <v>46.697812499999998</v>
+        <v>62.263750000000002</v>
       </c>
       <c r="Q12" s="1">
-        <v>46.46761875</v>
+        <v>61.956825000000002</v>
       </c>
       <c r="R12" s="1">
-        <v>48.744796874999992</v>
+        <v>64.993062499999994</v>
       </c>
       <c r="S12" s="1">
-        <v>57.72</v>
+        <v>76.959999999999994</v>
       </c>
       <c r="T12" s="1">
-        <v>62.911800000000014</v>
+        <v>83.882400000000018</v>
       </c>
       <c r="U12" s="1">
-        <v>75.973443750000001</v>
+        <v>101.29792499999999</v>
       </c>
       <c r="V12" s="1">
-        <v>76.753687499999984</v>
+        <v>102.33824999999999</v>
       </c>
       <c r="W12" s="1">
-        <v>71.393484375000014</v>
+        <v>95.191312500000009</v>
       </c>
       <c r="X12" s="1">
-        <v>61.989365625000005</v>
+        <v>82.652487500000007</v>
       </c>
       <c r="Y12" s="1">
-        <v>57.644371875000004</v>
+        <v>76.859162500000011</v>
       </c>
       <c r="Z12" s="1">
-        <v>55.192500000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+        <v>73.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2445,155 +2445,77 @@
         <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>51.330693750000009</v>
+        <v>68.440925000000007</v>
       </c>
       <c r="D13" s="1">
-        <v>49.363715625000012</v>
+        <v>65.818287500000011</v>
       </c>
       <c r="E13" s="1">
-        <v>46.791721875</v>
+        <v>62.388962499999998</v>
       </c>
       <c r="F13" s="1">
-        <v>45.955059375000012</v>
+        <v>61.273412500000013</v>
       </c>
       <c r="G13" s="1">
-        <v>44.954784375000003</v>
+        <v>59.939712499999999</v>
       </c>
       <c r="H13" s="1">
-        <v>44.185500000000005</v>
+        <v>58.914000000000009</v>
       </c>
       <c r="I13" s="1">
-        <v>51.281774999999996</v>
+        <v>68.375699999999995</v>
       </c>
       <c r="J13" s="1">
-        <v>60.29296875</v>
+        <v>80.390625</v>
       </c>
       <c r="K13" s="1">
-        <v>62.061028124999993</v>
+        <v>82.748037499999995</v>
       </c>
       <c r="L13" s="1">
-        <v>58.215712500000009</v>
+        <v>77.620950000000008</v>
       </c>
       <c r="M13" s="1">
-        <v>51.707250000000002</v>
+        <v>68.942999999999998</v>
       </c>
       <c r="N13" s="1">
-        <v>45.412078124999994</v>
+        <v>60.549437499999996</v>
       </c>
       <c r="O13" s="1">
-        <v>49.826109374999994</v>
+        <v>66.434812499999992</v>
       </c>
       <c r="P13" s="1">
-        <v>47.631768749999999</v>
+        <v>63.509025000000001</v>
       </c>
       <c r="Q13" s="1">
-        <v>45.045140625000002</v>
+        <v>60.060187500000005</v>
       </c>
       <c r="R13" s="1">
-        <v>52.849621874999997</v>
+        <v>70.466162499999996</v>
       </c>
       <c r="S13" s="1">
-        <v>55.411199999999994</v>
+        <v>73.881599999999992</v>
       </c>
       <c r="T13" s="1">
-        <v>66.188456250000002</v>
+        <v>88.251275000000007</v>
       </c>
       <c r="U13" s="1">
-        <v>75.235837500000002</v>
+        <v>100.31444999999999</v>
       </c>
       <c r="V13" s="1">
-        <v>75.291712499999988</v>
+        <v>100.38894999999998</v>
       </c>
       <c r="W13" s="1">
-        <v>66.541500000000013</v>
+        <v>88.722000000000008</v>
       </c>
       <c r="X13" s="1">
-        <v>62.628431250000006</v>
+        <v>83.504575000000003</v>
       </c>
       <c r="Y13" s="1">
-        <v>57.050100000000015</v>
+        <v>76.066800000000015</v>
       </c>
       <c r="Z13" s="1">
-        <v>54.640574999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
+        <v>72.854100000000003</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
